--- a/artfynd/A 27566-2025 artfynd.xlsx
+++ b/artfynd/A 27566-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1008,7 +1008,7 @@
         <v>125831667</v>
       </c>
       <c r="B5" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>125831666</v>
       </c>
       <c r="B6" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>125831653</v>
       </c>
       <c r="B7" t="n">
-        <v>92700</v>
+        <v>92707</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125831670</v>
+        <v>125831648</v>
       </c>
       <c r="B8" t="n">
-        <v>92502</v>
+        <v>98352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,21 +1307,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>887002</v>
+        <v>887197</v>
       </c>
       <c r="R8" t="n">
-        <v>7417848</v>
+        <v>7417856</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1393,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125831648</v>
+        <v>125831670</v>
       </c>
       <c r="B9" t="n">
-        <v>98345</v>
+        <v>92509</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1404,21 +1404,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>887197</v>
+        <v>887002</v>
       </c>
       <c r="R9" t="n">
-        <v>7417856</v>
+        <v>7417848</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
@@ -1493,7 +1493,7 @@
         <v>125831655</v>
       </c>
       <c r="B10" t="n">
-        <v>92700</v>
+        <v>92707</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>125831642</v>
       </c>
       <c r="B11" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>125831664</v>
       </c>
       <c r="B12" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>125831652</v>
       </c>
       <c r="B13" t="n">
-        <v>97208</v>
+        <v>97215</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2070,6 +2070,1563 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>125948975</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79974</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Pikku pullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>887138</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7417874</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125948997</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91387</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Pikku pullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>886998</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7417761</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>125948978</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92707</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Pikku pullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>886912</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7417840</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125948987</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78725</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Pikku pullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>886908</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7417842</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>125948981</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78726</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Pikku pullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>886920</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7417838</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125948980</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78726</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Pikku pullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>887085</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7417661</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125948979</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92707</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Pikku pullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>887056</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7417834</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125948966</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91227</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Pikku pullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>887008</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7417850</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125948982</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78726</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Pikku pullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>887109</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7417862</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125948983</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80070</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Pikku pullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>887190</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7417855</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125949005</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92509</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Pikku pullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>887242</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7417747</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125948964</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91399</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1588</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Violmussling</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Trichaptum laricinum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Pikku pullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>887119</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7417657</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125948974</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80071</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Pikku pullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>887197</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7417856</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125948998</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91387</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Pikku pullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>886916</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7417844</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125948968</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Pikku pullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>887185</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7417849</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Födosök gran</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>125948992</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98331</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Pikku pullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>887185</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7417856</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27566-2025 artfynd.xlsx
+++ b/artfynd/A 27566-2025 artfynd.xlsx
@@ -1781,10 +1781,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125831652</v>
+        <v>125831649</v>
       </c>
       <c r="B13" t="n">
-        <v>97215</v>
+        <v>79974</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1792,21 +1792,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>887148</v>
+        <v>887098</v>
       </c>
       <c r="R13" t="n">
-        <v>7417861</v>
+        <v>7417856</v>
       </c>
       <c r="S13" t="n">
         <v>2</v>
@@ -1878,10 +1878,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125831649</v>
+        <v>125831652</v>
       </c>
       <c r="B14" t="n">
-        <v>79974</v>
+        <v>97215</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1889,21 +1889,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>887098</v>
+        <v>887148</v>
       </c>
       <c r="R14" t="n">
-        <v>7417856</v>
+        <v>7417861</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125948981</v>
+        <v>125948979</v>
       </c>
       <c r="B20" t="n">
-        <v>78726</v>
+        <v>92707</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2471,21 +2471,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>886920</v>
+        <v>887056</v>
       </c>
       <c r="R20" t="n">
-        <v>7417838</v>
+        <v>7417834</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2557,10 +2557,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125948980</v>
+        <v>125948966</v>
       </c>
       <c r="B21" t="n">
-        <v>78726</v>
+        <v>91227</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2568,21 +2568,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>887085</v>
+        <v>887008</v>
       </c>
       <c r="R21" t="n">
-        <v>7417661</v>
+        <v>7417850</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125948979</v>
+        <v>125948981</v>
       </c>
       <c r="B22" t="n">
-        <v>92707</v>
+        <v>78726</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2665,21 +2665,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>887056</v>
+        <v>886920</v>
       </c>
       <c r="R22" t="n">
-        <v>7417834</v>
+        <v>7417838</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2751,10 +2751,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125948966</v>
+        <v>125948980</v>
       </c>
       <c r="B23" t="n">
-        <v>91227</v>
+        <v>78726</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2762,21 +2762,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>887008</v>
+        <v>887085</v>
       </c>
       <c r="R23" t="n">
-        <v>7417850</v>
+        <v>7417661</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>

--- a/artfynd/A 27566-2025 artfynd.xlsx
+++ b/artfynd/A 27566-2025 artfynd.xlsx
@@ -1008,7 +1008,7 @@
         <v>125831667</v>
       </c>
       <c r="B5" t="n">
-        <v>92509</v>
+        <v>92510</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>125831666</v>
       </c>
       <c r="B6" t="n">
-        <v>92509</v>
+        <v>92510</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>125831653</v>
       </c>
       <c r="B7" t="n">
-        <v>92707</v>
+        <v>92708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125831648</v>
+        <v>125831670</v>
       </c>
       <c r="B8" t="n">
-        <v>98352</v>
+        <v>92510</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,21 +1307,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>887197</v>
+        <v>887002</v>
       </c>
       <c r="R8" t="n">
-        <v>7417856</v>
+        <v>7417848</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1393,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125831670</v>
+        <v>125831648</v>
       </c>
       <c r="B9" t="n">
-        <v>92509</v>
+        <v>98353</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1404,21 +1404,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>887002</v>
+        <v>887197</v>
       </c>
       <c r="R9" t="n">
-        <v>7417848</v>
+        <v>7417856</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
@@ -1493,7 +1493,7 @@
         <v>125831655</v>
       </c>
       <c r="B10" t="n">
-        <v>92707</v>
+        <v>92708</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>125831642</v>
       </c>
       <c r="B11" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>125831664</v>
       </c>
       <c r="B12" t="n">
-        <v>92509</v>
+        <v>92510</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>125831649</v>
       </c>
       <c r="B13" t="n">
-        <v>79974</v>
+        <v>79975</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>125831652</v>
       </c>
       <c r="B14" t="n">
-        <v>97215</v>
+        <v>97216</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>125948975</v>
       </c>
       <c r="B16" t="n">
-        <v>79974</v>
+        <v>79975</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>125948997</v>
       </c>
       <c r="B17" t="n">
-        <v>91387</v>
+        <v>91388</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>125948978</v>
       </c>
       <c r="B18" t="n">
-        <v>92707</v>
+        <v>92708</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>125948987</v>
       </c>
       <c r="B19" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>125948979</v>
       </c>
       <c r="B20" t="n">
-        <v>92707</v>
+        <v>92708</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>125948966</v>
       </c>
       <c r="B21" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>125948981</v>
       </c>
       <c r="B22" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>125948980</v>
       </c>
       <c r="B23" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>125948982</v>
       </c>
       <c r="B24" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         <v>125948983</v>
       </c>
       <c r="B25" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>125949005</v>
       </c>
       <c r="B26" t="n">
-        <v>92509</v>
+        <v>92510</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>125948964</v>
       </c>
       <c r="B27" t="n">
-        <v>91399</v>
+        <v>91400</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>125948974</v>
       </c>
       <c r="B28" t="n">
-        <v>80071</v>
+        <v>80072</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>125948998</v>
       </c>
       <c r="B29" t="n">
-        <v>91387</v>
+        <v>91388</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>125948992</v>
       </c>
       <c r="B31" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 27566-2025 artfynd.xlsx
+++ b/artfynd/A 27566-2025 artfynd.xlsx
@@ -1008,7 +1008,7 @@
         <v>125831667</v>
       </c>
       <c r="B5" t="n">
-        <v>92510</v>
+        <v>92518</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>125831666</v>
       </c>
       <c r="B6" t="n">
-        <v>92510</v>
+        <v>92518</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>125831653</v>
       </c>
       <c r="B7" t="n">
-        <v>92708</v>
+        <v>92710</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125831670</v>
+        <v>125831648</v>
       </c>
       <c r="B8" t="n">
-        <v>92510</v>
+        <v>98355</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,21 +1307,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>887002</v>
+        <v>887197</v>
       </c>
       <c r="R8" t="n">
-        <v>7417848</v>
+        <v>7417856</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1393,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125831648</v>
+        <v>125831670</v>
       </c>
       <c r="B9" t="n">
-        <v>98353</v>
+        <v>92518</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1404,21 +1404,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>887197</v>
+        <v>887002</v>
       </c>
       <c r="R9" t="n">
-        <v>7417856</v>
+        <v>7417848</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
@@ -1493,7 +1493,7 @@
         <v>125831655</v>
       </c>
       <c r="B10" t="n">
-        <v>92708</v>
+        <v>92710</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>125831664</v>
       </c>
       <c r="B12" t="n">
-        <v>92510</v>
+        <v>92518</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>125831652</v>
       </c>
       <c r="B14" t="n">
-        <v>97216</v>
+        <v>97218</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>125948997</v>
       </c>
       <c r="B17" t="n">
-        <v>91388</v>
+        <v>91389</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>125948978</v>
       </c>
       <c r="B18" t="n">
-        <v>92708</v>
+        <v>92710</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125948979</v>
+        <v>125948981</v>
       </c>
       <c r="B20" t="n">
-        <v>92708</v>
+        <v>78727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2471,21 +2471,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>887056</v>
+        <v>886920</v>
       </c>
       <c r="R20" t="n">
-        <v>7417834</v>
+        <v>7417838</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2557,10 +2557,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125948966</v>
+        <v>125948980</v>
       </c>
       <c r="B21" t="n">
-        <v>91228</v>
+        <v>78727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2568,21 +2568,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>887008</v>
+        <v>887085</v>
       </c>
       <c r="R21" t="n">
-        <v>7417850</v>
+        <v>7417661</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125948981</v>
+        <v>125948979</v>
       </c>
       <c r="B22" t="n">
-        <v>78727</v>
+        <v>92710</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2665,21 +2665,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>886920</v>
+        <v>887056</v>
       </c>
       <c r="R22" t="n">
-        <v>7417838</v>
+        <v>7417834</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2751,10 +2751,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125948980</v>
+        <v>125948966</v>
       </c>
       <c r="B23" t="n">
-        <v>78727</v>
+        <v>91228</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2762,21 +2762,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>887085</v>
+        <v>887008</v>
       </c>
       <c r="R23" t="n">
-        <v>7417661</v>
+        <v>7417850</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3045,7 +3045,7 @@
         <v>125949005</v>
       </c>
       <c r="B26" t="n">
-        <v>92510</v>
+        <v>92518</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3139,10 +3139,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125948964</v>
+        <v>125948974</v>
       </c>
       <c r="B27" t="n">
-        <v>91400</v>
+        <v>80072</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3150,21 +3150,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1588</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3174,10 +3174,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>887119</v>
+        <v>887197</v>
       </c>
       <c r="R27" t="n">
-        <v>7417657</v>
+        <v>7417856</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3236,10 +3236,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125948974</v>
+        <v>125948964</v>
       </c>
       <c r="B28" t="n">
-        <v>80072</v>
+        <v>91403</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3247,21 +3247,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>1588</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3271,10 +3271,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>887197</v>
+        <v>887119</v>
       </c>
       <c r="R28" t="n">
-        <v>7417856</v>
+        <v>7417657</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3336,7 +3336,7 @@
         <v>125948998</v>
       </c>
       <c r="B29" t="n">
-        <v>91388</v>
+        <v>91389</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>125948992</v>
       </c>
       <c r="B31" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 27566-2025 artfynd.xlsx
+++ b/artfynd/A 27566-2025 artfynd.xlsx
@@ -1008,7 +1008,7 @@
         <v>125831667</v>
       </c>
       <c r="B5" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>125831666</v>
       </c>
       <c r="B6" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>125831653</v>
       </c>
       <c r="B7" t="n">
-        <v>92710</v>
+        <v>92714</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>125831648</v>
       </c>
       <c r="B8" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>125831670</v>
       </c>
       <c r="B9" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>125831655</v>
       </c>
       <c r="B10" t="n">
-        <v>92710</v>
+        <v>92714</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>125831642</v>
       </c>
       <c r="B11" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>125831664</v>
       </c>
       <c r="B12" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,10 +1781,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125831649</v>
+        <v>125831652</v>
       </c>
       <c r="B13" t="n">
-        <v>79975</v>
+        <v>97222</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1792,21 +1792,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>221941</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>887098</v>
+        <v>887148</v>
       </c>
       <c r="R13" t="n">
-        <v>7417856</v>
+        <v>7417861</v>
       </c>
       <c r="S13" t="n">
         <v>2</v>
@@ -1878,10 +1878,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125831652</v>
+        <v>125831649</v>
       </c>
       <c r="B14" t="n">
-        <v>97218</v>
+        <v>79979</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1889,21 +1889,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>887148</v>
+        <v>887098</v>
       </c>
       <c r="R14" t="n">
-        <v>7417861</v>
+        <v>7417856</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
@@ -2075,7 +2075,7 @@
         <v>125948975</v>
       </c>
       <c r="B16" t="n">
-        <v>79975</v>
+        <v>79979</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>125948997</v>
       </c>
       <c r="B17" t="n">
-        <v>91389</v>
+        <v>91393</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>125948978</v>
       </c>
       <c r="B18" t="n">
-        <v>92710</v>
+        <v>92714</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>125948987</v>
       </c>
       <c r="B19" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125948981</v>
+        <v>125948979</v>
       </c>
       <c r="B20" t="n">
-        <v>78727</v>
+        <v>92714</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2471,21 +2471,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>886920</v>
+        <v>887056</v>
       </c>
       <c r="R20" t="n">
-        <v>7417838</v>
+        <v>7417834</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2557,10 +2557,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125948980</v>
+        <v>125948966</v>
       </c>
       <c r="B21" t="n">
-        <v>78727</v>
+        <v>91232</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2568,21 +2568,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>887085</v>
+        <v>887008</v>
       </c>
       <c r="R21" t="n">
-        <v>7417661</v>
+        <v>7417850</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125948979</v>
+        <v>125948981</v>
       </c>
       <c r="B22" t="n">
-        <v>92710</v>
+        <v>78731</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2665,21 +2665,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>887056</v>
+        <v>886920</v>
       </c>
       <c r="R22" t="n">
-        <v>7417834</v>
+        <v>7417838</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2751,10 +2751,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125948966</v>
+        <v>125948980</v>
       </c>
       <c r="B23" t="n">
-        <v>91228</v>
+        <v>78731</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2762,21 +2762,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>887008</v>
+        <v>887085</v>
       </c>
       <c r="R23" t="n">
-        <v>7417850</v>
+        <v>7417661</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2851,7 +2851,7 @@
         <v>125948982</v>
       </c>
       <c r="B24" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         <v>125948983</v>
       </c>
       <c r="B25" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>125949005</v>
       </c>
       <c r="B26" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>125948974</v>
       </c>
       <c r="B27" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>125948964</v>
       </c>
       <c r="B28" t="n">
-        <v>91403</v>
+        <v>91407</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>125948998</v>
       </c>
       <c r="B29" t="n">
-        <v>91389</v>
+        <v>91393</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>125948992</v>
       </c>
       <c r="B31" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 27566-2025 artfynd.xlsx
+++ b/artfynd/A 27566-2025 artfynd.xlsx
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125831648</v>
+        <v>125831670</v>
       </c>
       <c r="B8" t="n">
-        <v>98359</v>
+        <v>92522</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,21 +1307,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>887197</v>
+        <v>887002</v>
       </c>
       <c r="R8" t="n">
-        <v>7417856</v>
+        <v>7417848</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1393,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125831670</v>
+        <v>125831648</v>
       </c>
       <c r="B9" t="n">
-        <v>92522</v>
+        <v>98360</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1404,21 +1404,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>887002</v>
+        <v>887197</v>
       </c>
       <c r="R9" t="n">
-        <v>7417848</v>
+        <v>7417856</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
@@ -1784,7 +1784,7 @@
         <v>125831652</v>
       </c>
       <c r="B13" t="n">
-        <v>97222</v>
+        <v>97223</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3139,10 +3139,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125948974</v>
+        <v>125948964</v>
       </c>
       <c r="B27" t="n">
-        <v>80076</v>
+        <v>91407</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3150,21 +3150,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>1588</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3174,10 +3174,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>887197</v>
+        <v>887119</v>
       </c>
       <c r="R27" t="n">
-        <v>7417856</v>
+        <v>7417657</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3236,10 +3236,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125948964</v>
+        <v>125948974</v>
       </c>
       <c r="B28" t="n">
-        <v>91407</v>
+        <v>80076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3247,21 +3247,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1588</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3271,10 +3271,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>887119</v>
+        <v>887197</v>
       </c>
       <c r="R28" t="n">
-        <v>7417657</v>
+        <v>7417856</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3535,7 +3535,7 @@
         <v>125948992</v>
       </c>
       <c r="B31" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 27566-2025 artfynd.xlsx
+++ b/artfynd/A 27566-2025 artfynd.xlsx
@@ -1008,7 +1008,7 @@
         <v>125831667</v>
       </c>
       <c r="B5" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>125831666</v>
       </c>
       <c r="B6" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>125831653</v>
       </c>
       <c r="B7" t="n">
-        <v>92714</v>
+        <v>92716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>125831670</v>
       </c>
       <c r="B8" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>125831648</v>
       </c>
       <c r="B9" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>125831655</v>
       </c>
       <c r="B10" t="n">
-        <v>92714</v>
+        <v>92716</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>125831642</v>
       </c>
       <c r="B11" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>125831664</v>
       </c>
       <c r="B12" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,10 +1781,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125831652</v>
+        <v>125831649</v>
       </c>
       <c r="B13" t="n">
-        <v>97223</v>
+        <v>79980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1792,21 +1792,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>887148</v>
+        <v>887098</v>
       </c>
       <c r="R13" t="n">
-        <v>7417861</v>
+        <v>7417856</v>
       </c>
       <c r="S13" t="n">
         <v>2</v>
@@ -1878,10 +1878,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125831649</v>
+        <v>125831652</v>
       </c>
       <c r="B14" t="n">
-        <v>79979</v>
+        <v>97225</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1889,21 +1889,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>887098</v>
+        <v>887148</v>
       </c>
       <c r="R14" t="n">
-        <v>7417856</v>
+        <v>7417861</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
@@ -1978,7 +1978,7 @@
         <v>125831645</v>
       </c>
       <c r="B15" t="n">
-        <v>57811</v>
+        <v>57812</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>125948975</v>
       </c>
       <c r="B16" t="n">
-        <v>79979</v>
+        <v>79980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>125948997</v>
       </c>
       <c r="B17" t="n">
-        <v>91393</v>
+        <v>91395</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>125948978</v>
       </c>
       <c r="B18" t="n">
-        <v>92714</v>
+        <v>92716</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>125948987</v>
       </c>
       <c r="B19" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125948979</v>
+        <v>125948966</v>
       </c>
       <c r="B20" t="n">
-        <v>92714</v>
+        <v>91234</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2471,21 +2471,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2079</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>887056</v>
+        <v>887008</v>
       </c>
       <c r="R20" t="n">
-        <v>7417834</v>
+        <v>7417850</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2557,10 +2557,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125948966</v>
+        <v>125948979</v>
       </c>
       <c r="B21" t="n">
-        <v>91232</v>
+        <v>92716</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2568,21 +2568,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>2079</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>887008</v>
+        <v>887056</v>
       </c>
       <c r="R21" t="n">
-        <v>7417850</v>
+        <v>7417834</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2657,7 +2657,7 @@
         <v>125948981</v>
       </c>
       <c r="B22" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>125948980</v>
       </c>
       <c r="B23" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>125948982</v>
       </c>
       <c r="B24" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         <v>125948983</v>
       </c>
       <c r="B25" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>125949005</v>
       </c>
       <c r="B26" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>125948964</v>
       </c>
       <c r="B27" t="n">
-        <v>91407</v>
+        <v>91409</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>125948974</v>
       </c>
       <c r="B28" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>125948998</v>
       </c>
       <c r="B29" t="n">
-        <v>91393</v>
+        <v>91395</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>125948968</v>
       </c>
       <c r="B30" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>125948992</v>
       </c>
       <c r="B31" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 27566-2025 artfynd.xlsx
+++ b/artfynd/A 27566-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1008,7 +1008,7 @@
         <v>125831667</v>
       </c>
       <c r="B5" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>125831666</v>
       </c>
       <c r="B6" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>125831653</v>
       </c>
       <c r="B7" t="n">
-        <v>92716</v>
+        <v>92718</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>125831670</v>
       </c>
       <c r="B8" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>125831648</v>
       </c>
       <c r="B9" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>125831655</v>
       </c>
       <c r="B10" t="n">
-        <v>92716</v>
+        <v>92718</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>125831642</v>
       </c>
       <c r="B11" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>125831664</v>
       </c>
       <c r="B12" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,10 +1781,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125831649</v>
+        <v>125831652</v>
       </c>
       <c r="B13" t="n">
-        <v>79980</v>
+        <v>97227</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1792,21 +1792,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>221941</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>887098</v>
+        <v>887148</v>
       </c>
       <c r="R13" t="n">
-        <v>7417856</v>
+        <v>7417861</v>
       </c>
       <c r="S13" t="n">
         <v>2</v>
@@ -1878,10 +1878,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125831652</v>
+        <v>125831649</v>
       </c>
       <c r="B14" t="n">
-        <v>97225</v>
+        <v>79980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1889,21 +1889,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>887148</v>
+        <v>887098</v>
       </c>
       <c r="R14" t="n">
-        <v>7417861</v>
+        <v>7417856</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
@@ -2172,7 +2172,7 @@
         <v>125948997</v>
       </c>
       <c r="B17" t="n">
-        <v>91395</v>
+        <v>91397</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>125948978</v>
       </c>
       <c r="B18" t="n">
-        <v>92716</v>
+        <v>92718</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>125948966</v>
       </c>
       <c r="B20" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>125948979</v>
       </c>
       <c r="B21" t="n">
-        <v>92716</v>
+        <v>92718</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125948981</v>
+        <v>125948980</v>
       </c>
       <c r="B22" t="n">
         <v>78732</v>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>886920</v>
+        <v>887085</v>
       </c>
       <c r="R22" t="n">
-        <v>7417838</v>
+        <v>7417661</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2751,7 +2751,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125948980</v>
+        <v>125948981</v>
       </c>
       <c r="B23" t="n">
         <v>78732</v>
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>887085</v>
+        <v>886920</v>
       </c>
       <c r="R23" t="n">
-        <v>7417661</v>
+        <v>7417838</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3045,7 +3045,7 @@
         <v>125949005</v>
       </c>
       <c r="B26" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>125948964</v>
       </c>
       <c r="B27" t="n">
-        <v>91409</v>
+        <v>91411</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>125948998</v>
       </c>
       <c r="B29" t="n">
-        <v>91395</v>
+        <v>91397</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>125948992</v>
       </c>
       <c r="B31" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3626,6 +3626,103 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126254767</v>
+      </c>
+      <c r="B32" t="n">
+        <v>92526</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Pullinkinrova, Nb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>887314</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7417479</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27566-2025 artfynd.xlsx
+++ b/artfynd/A 27566-2025 artfynd.xlsx
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125831670</v>
+        <v>125831648</v>
       </c>
       <c r="B8" t="n">
-        <v>92526</v>
+        <v>98364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,21 +1307,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>887002</v>
+        <v>887197</v>
       </c>
       <c r="R8" t="n">
-        <v>7417848</v>
+        <v>7417856</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1393,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125831648</v>
+        <v>125831670</v>
       </c>
       <c r="B9" t="n">
-        <v>98364</v>
+        <v>92526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1404,21 +1404,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>887197</v>
+        <v>887002</v>
       </c>
       <c r="R9" t="n">
-        <v>7417856</v>
+        <v>7417848</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>

--- a/artfynd/A 27566-2025 artfynd.xlsx
+++ b/artfynd/A 27566-2025 artfynd.xlsx
@@ -1008,7 +1008,7 @@
         <v>125831667</v>
       </c>
       <c r="B5" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>125831666</v>
       </c>
       <c r="B6" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>125831653</v>
       </c>
       <c r="B7" t="n">
-        <v>92718</v>
+        <v>92720</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125831648</v>
+        <v>125831670</v>
       </c>
       <c r="B8" t="n">
-        <v>98364</v>
+        <v>92528</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,21 +1307,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>887197</v>
+        <v>887002</v>
       </c>
       <c r="R8" t="n">
-        <v>7417856</v>
+        <v>7417848</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1393,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125831670</v>
+        <v>125831648</v>
       </c>
       <c r="B9" t="n">
-        <v>92526</v>
+        <v>98366</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1404,21 +1404,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>887002</v>
+        <v>887197</v>
       </c>
       <c r="R9" t="n">
-        <v>7417848</v>
+        <v>7417856</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
@@ -1493,7 +1493,7 @@
         <v>125831655</v>
       </c>
       <c r="B10" t="n">
-        <v>92718</v>
+        <v>92720</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>125831642</v>
       </c>
       <c r="B11" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>125831664</v>
       </c>
       <c r="B12" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,10 +1781,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125831652</v>
+        <v>125831649</v>
       </c>
       <c r="B13" t="n">
-        <v>97227</v>
+        <v>79980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1792,21 +1792,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>887148</v>
+        <v>887098</v>
       </c>
       <c r="R13" t="n">
-        <v>7417861</v>
+        <v>7417856</v>
       </c>
       <c r="S13" t="n">
         <v>2</v>
@@ -1878,10 +1878,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125831649</v>
+        <v>125831652</v>
       </c>
       <c r="B14" t="n">
-        <v>79980</v>
+        <v>97229</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1889,21 +1889,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>887098</v>
+        <v>887148</v>
       </c>
       <c r="R14" t="n">
-        <v>7417856</v>
+        <v>7417861</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
@@ -2172,7 +2172,7 @@
         <v>125948997</v>
       </c>
       <c r="B17" t="n">
-        <v>91397</v>
+        <v>91399</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>125948978</v>
       </c>
       <c r="B18" t="n">
-        <v>92718</v>
+        <v>92720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125948966</v>
+        <v>125948979</v>
       </c>
       <c r="B20" t="n">
-        <v>91236</v>
+        <v>92720</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2471,21 +2471,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>2079</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>887008</v>
+        <v>887056</v>
       </c>
       <c r="R20" t="n">
-        <v>7417850</v>
+        <v>7417834</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2557,10 +2557,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125948979</v>
+        <v>125948966</v>
       </c>
       <c r="B21" t="n">
-        <v>92718</v>
+        <v>91238</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2568,21 +2568,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2079</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>887056</v>
+        <v>887008</v>
       </c>
       <c r="R21" t="n">
-        <v>7417834</v>
+        <v>7417850</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3045,7 +3045,7 @@
         <v>125949005</v>
       </c>
       <c r="B26" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>125948964</v>
       </c>
       <c r="B27" t="n">
-        <v>91411</v>
+        <v>91413</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>125948998</v>
       </c>
       <c r="B29" t="n">
-        <v>91397</v>
+        <v>91399</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>125948992</v>
       </c>
       <c r="B31" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>126254767</v>
       </c>
       <c r="B32" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 27566-2025 artfynd.xlsx
+++ b/artfynd/A 27566-2025 artfynd.xlsx
@@ -1008,7 +1008,7 @@
         <v>125831667</v>
       </c>
       <c r="B5" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>125831666</v>
       </c>
       <c r="B6" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>125831653</v>
       </c>
       <c r="B7" t="n">
-        <v>92720</v>
+        <v>92724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>125831670</v>
       </c>
       <c r="B8" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>125831648</v>
       </c>
       <c r="B9" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>125831655</v>
       </c>
       <c r="B10" t="n">
-        <v>92720</v>
+        <v>92724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>125831642</v>
       </c>
       <c r="B11" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>125831664</v>
       </c>
       <c r="B12" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,10 +1781,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125831649</v>
+        <v>125831652</v>
       </c>
       <c r="B13" t="n">
-        <v>79980</v>
+        <v>97233</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1792,21 +1792,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>221941</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>887098</v>
+        <v>887148</v>
       </c>
       <c r="R13" t="n">
-        <v>7417856</v>
+        <v>7417861</v>
       </c>
       <c r="S13" t="n">
         <v>2</v>
@@ -1878,10 +1878,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125831652</v>
+        <v>125831649</v>
       </c>
       <c r="B14" t="n">
-        <v>97229</v>
+        <v>79984</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1889,21 +1889,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>887148</v>
+        <v>887098</v>
       </c>
       <c r="R14" t="n">
-        <v>7417861</v>
+        <v>7417856</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
@@ -1978,7 +1978,7 @@
         <v>125831645</v>
       </c>
       <c r="B15" t="n">
-        <v>57812</v>
+        <v>57816</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>125948975</v>
       </c>
       <c r="B16" t="n">
-        <v>79980</v>
+        <v>79984</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>125948997</v>
       </c>
       <c r="B17" t="n">
-        <v>91399</v>
+        <v>91403</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>125948978</v>
       </c>
       <c r="B18" t="n">
-        <v>92720</v>
+        <v>92724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>125948987</v>
       </c>
       <c r="B19" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125948979</v>
+        <v>125948966</v>
       </c>
       <c r="B20" t="n">
-        <v>92720</v>
+        <v>91242</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2471,21 +2471,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2079</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>887056</v>
+        <v>887008</v>
       </c>
       <c r="R20" t="n">
-        <v>7417834</v>
+        <v>7417850</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2557,10 +2557,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125948966</v>
+        <v>125948980</v>
       </c>
       <c r="B21" t="n">
-        <v>91238</v>
+        <v>78736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2568,21 +2568,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>887008</v>
+        <v>887085</v>
       </c>
       <c r="R21" t="n">
-        <v>7417850</v>
+        <v>7417661</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125948980</v>
+        <v>125948981</v>
       </c>
       <c r="B22" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>887085</v>
+        <v>886920</v>
       </c>
       <c r="R22" t="n">
-        <v>7417661</v>
+        <v>7417838</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2751,10 +2751,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125948981</v>
+        <v>125948979</v>
       </c>
       <c r="B23" t="n">
-        <v>78732</v>
+        <v>92724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2762,21 +2762,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>886920</v>
+        <v>887056</v>
       </c>
       <c r="R23" t="n">
-        <v>7417838</v>
+        <v>7417834</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2851,7 +2851,7 @@
         <v>125948982</v>
       </c>
       <c r="B24" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         <v>125948983</v>
       </c>
       <c r="B25" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>125949005</v>
       </c>
       <c r="B26" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>125948964</v>
       </c>
       <c r="B27" t="n">
-        <v>91413</v>
+        <v>91417</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>125948974</v>
       </c>
       <c r="B28" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>125948998</v>
       </c>
       <c r="B29" t="n">
-        <v>91399</v>
+        <v>91403</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>125948968</v>
       </c>
       <c r="B30" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>125948992</v>
       </c>
       <c r="B31" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>126254767</v>
       </c>
       <c r="B32" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 27566-2025 artfynd.xlsx
+++ b/artfynd/A 27566-2025 artfynd.xlsx
@@ -2460,10 +2460,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125948966</v>
+        <v>125948979</v>
       </c>
       <c r="B20" t="n">
-        <v>91242</v>
+        <v>92724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2471,21 +2471,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>2079</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>887008</v>
+        <v>887056</v>
       </c>
       <c r="R20" t="n">
-        <v>7417850</v>
+        <v>7417834</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2557,10 +2557,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125948980</v>
+        <v>125948966</v>
       </c>
       <c r="B21" t="n">
-        <v>78736</v>
+        <v>91242</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2568,21 +2568,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>887085</v>
+        <v>887008</v>
       </c>
       <c r="R21" t="n">
-        <v>7417661</v>
+        <v>7417850</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2654,7 +2654,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125948981</v>
+        <v>125948980</v>
       </c>
       <c r="B22" t="n">
         <v>78736</v>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>886920</v>
+        <v>887085</v>
       </c>
       <c r="R22" t="n">
-        <v>7417838</v>
+        <v>7417661</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2751,10 +2751,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125948979</v>
+        <v>125948981</v>
       </c>
       <c r="B23" t="n">
-        <v>92724</v>
+        <v>78736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2762,21 +2762,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>887056</v>
+        <v>886920</v>
       </c>
       <c r="R23" t="n">
-        <v>7417834</v>
+        <v>7417838</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>

--- a/artfynd/A 27566-2025 artfynd.xlsx
+++ b/artfynd/A 27566-2025 artfynd.xlsx
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125831670</v>
+        <v>125831648</v>
       </c>
       <c r="B8" t="n">
-        <v>92532</v>
+        <v>98373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,21 +1307,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>887002</v>
+        <v>887197</v>
       </c>
       <c r="R8" t="n">
-        <v>7417848</v>
+        <v>7417856</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1393,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125831648</v>
+        <v>125831670</v>
       </c>
       <c r="B9" t="n">
-        <v>98370</v>
+        <v>92532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1404,21 +1404,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>887197</v>
+        <v>887002</v>
       </c>
       <c r="R9" t="n">
-        <v>7417856</v>
+        <v>7417848</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
@@ -1781,10 +1781,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125831652</v>
+        <v>125831649</v>
       </c>
       <c r="B13" t="n">
-        <v>97233</v>
+        <v>79984</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1792,21 +1792,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>887148</v>
+        <v>887098</v>
       </c>
       <c r="R13" t="n">
-        <v>7417861</v>
+        <v>7417856</v>
       </c>
       <c r="S13" t="n">
         <v>2</v>
@@ -1878,10 +1878,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125831649</v>
+        <v>125831652</v>
       </c>
       <c r="B14" t="n">
-        <v>79984</v>
+        <v>97236</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1889,21 +1889,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>887098</v>
+        <v>887148</v>
       </c>
       <c r="R14" t="n">
-        <v>7417856</v>
+        <v>7417861</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
@@ -2654,7 +2654,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125948980</v>
+        <v>125948981</v>
       </c>
       <c r="B22" t="n">
         <v>78736</v>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>887085</v>
+        <v>886920</v>
       </c>
       <c r="R22" t="n">
-        <v>7417661</v>
+        <v>7417838</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2751,7 +2751,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125948981</v>
+        <v>125948980</v>
       </c>
       <c r="B23" t="n">
         <v>78736</v>
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>886920</v>
+        <v>887085</v>
       </c>
       <c r="R23" t="n">
-        <v>7417838</v>
+        <v>7417661</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3535,7 +3535,7 @@
         <v>125948992</v>
       </c>
       <c r="B31" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 27566-2025 artfynd.xlsx
+++ b/artfynd/A 27566-2025 artfynd.xlsx
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125831648</v>
+        <v>125831670</v>
       </c>
       <c r="B8" t="n">
-        <v>98373</v>
+        <v>92532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,21 +1307,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>887197</v>
+        <v>887002</v>
       </c>
       <c r="R8" t="n">
-        <v>7417856</v>
+        <v>7417848</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1393,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125831670</v>
+        <v>125831648</v>
       </c>
       <c r="B9" t="n">
-        <v>92532</v>
+        <v>98373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1404,21 +1404,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>887002</v>
+        <v>887197</v>
       </c>
       <c r="R9" t="n">
-        <v>7417848</v>
+        <v>7417856</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>

--- a/artfynd/A 27566-2025 artfynd.xlsx
+++ b/artfynd/A 27566-2025 artfynd.xlsx
@@ -1008,7 +1008,7 @@
         <v>125831667</v>
       </c>
       <c r="B5" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>125831666</v>
       </c>
       <c r="B6" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>125831653</v>
       </c>
       <c r="B7" t="n">
-        <v>92724</v>
+        <v>92727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>125831670</v>
       </c>
       <c r="B8" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>125831648</v>
       </c>
       <c r="B9" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>125831655</v>
       </c>
       <c r="B10" t="n">
-        <v>92724</v>
+        <v>92727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>125831642</v>
       </c>
       <c r="B11" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>125831664</v>
       </c>
       <c r="B12" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>125831649</v>
       </c>
       <c r="B13" t="n">
-        <v>79984</v>
+        <v>79987</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>125831652</v>
       </c>
       <c r="B14" t="n">
-        <v>97236</v>
+        <v>97245</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>125831645</v>
       </c>
       <c r="B15" t="n">
-        <v>57816</v>
+        <v>57817</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>125948975</v>
       </c>
       <c r="B16" t="n">
-        <v>79984</v>
+        <v>79987</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>125948997</v>
       </c>
       <c r="B17" t="n">
-        <v>91403</v>
+        <v>91406</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>125948978</v>
       </c>
       <c r="B18" t="n">
-        <v>92724</v>
+        <v>92727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>125948987</v>
       </c>
       <c r="B19" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125948979</v>
+        <v>125948981</v>
       </c>
       <c r="B20" t="n">
-        <v>92724</v>
+        <v>78739</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2471,21 +2471,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>887056</v>
+        <v>886920</v>
       </c>
       <c r="R20" t="n">
-        <v>7417834</v>
+        <v>7417838</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2557,10 +2557,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125948966</v>
+        <v>125948980</v>
       </c>
       <c r="B21" t="n">
-        <v>91242</v>
+        <v>78739</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2568,21 +2568,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>887008</v>
+        <v>887085</v>
       </c>
       <c r="R21" t="n">
-        <v>7417850</v>
+        <v>7417661</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125948981</v>
+        <v>125948979</v>
       </c>
       <c r="B22" t="n">
-        <v>78736</v>
+        <v>92727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2665,21 +2665,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>886920</v>
+        <v>887056</v>
       </c>
       <c r="R22" t="n">
-        <v>7417838</v>
+        <v>7417834</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2751,10 +2751,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125948980</v>
+        <v>125948966</v>
       </c>
       <c r="B23" t="n">
-        <v>78736</v>
+        <v>91245</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2762,21 +2762,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>887085</v>
+        <v>887008</v>
       </c>
       <c r="R23" t="n">
-        <v>7417661</v>
+        <v>7417850</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2851,7 +2851,7 @@
         <v>125948982</v>
       </c>
       <c r="B24" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         <v>125948983</v>
       </c>
       <c r="B25" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>125949005</v>
       </c>
       <c r="B26" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>125948964</v>
       </c>
       <c r="B27" t="n">
-        <v>91417</v>
+        <v>91420</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>125948974</v>
       </c>
       <c r="B28" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>125948998</v>
       </c>
       <c r="B29" t="n">
-        <v>91403</v>
+        <v>91406</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>125948968</v>
       </c>
       <c r="B30" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>125948992</v>
       </c>
       <c r="B31" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>126254767</v>
       </c>
       <c r="B32" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 27566-2025 artfynd.xlsx
+++ b/artfynd/A 27566-2025 artfynd.xlsx
@@ -2460,10 +2460,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125948981</v>
+        <v>125948979</v>
       </c>
       <c r="B20" t="n">
-        <v>78739</v>
+        <v>92727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2471,21 +2471,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>886920</v>
+        <v>887056</v>
       </c>
       <c r="R20" t="n">
-        <v>7417838</v>
+        <v>7417834</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2557,10 +2557,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125948980</v>
+        <v>125948966</v>
       </c>
       <c r="B21" t="n">
-        <v>78739</v>
+        <v>91245</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2568,21 +2568,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>887085</v>
+        <v>887008</v>
       </c>
       <c r="R21" t="n">
-        <v>7417661</v>
+        <v>7417850</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125948979</v>
+        <v>125948981</v>
       </c>
       <c r="B22" t="n">
-        <v>92727</v>
+        <v>78739</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2665,21 +2665,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>887056</v>
+        <v>886920</v>
       </c>
       <c r="R22" t="n">
-        <v>7417834</v>
+        <v>7417838</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2751,10 +2751,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125948966</v>
+        <v>125948980</v>
       </c>
       <c r="B23" t="n">
-        <v>91245</v>
+        <v>78739</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2762,21 +2762,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>887008</v>
+        <v>887085</v>
       </c>
       <c r="R23" t="n">
-        <v>7417850</v>
+        <v>7417661</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>

--- a/artfynd/A 27566-2025 artfynd.xlsx
+++ b/artfynd/A 27566-2025 artfynd.xlsx
@@ -3729,7 +3729,7 @@
         <v>126913715</v>
       </c>
       <c r="B33" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>126914389</v>
       </c>
       <c r="B34" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>126913924</v>
       </c>
       <c r="B35" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>126913728</v>
       </c>
       <c r="B36" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>126913909</v>
       </c>
       <c r="B37" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>126914390</v>
       </c>
       <c r="B38" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>126913899</v>
       </c>
       <c r="B39" t="n">
-        <v>92727</v>
+        <v>92802</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 27566-2025 artfynd.xlsx
+++ b/artfynd/A 27566-2025 artfynd.xlsx
@@ -3729,7 +3729,7 @@
         <v>126913715</v>
       </c>
       <c r="B33" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>126914389</v>
       </c>
       <c r="B34" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>126913924</v>
       </c>
       <c r="B35" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>126913728</v>
       </c>
       <c r="B36" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>126913909</v>
       </c>
       <c r="B37" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>126914390</v>
       </c>
       <c r="B38" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>126913899</v>
       </c>
       <c r="B39" t="n">
-        <v>92802</v>
+        <v>92808</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 27566-2025 artfynd.xlsx
+++ b/artfynd/A 27566-2025 artfynd.xlsx
@@ -3830,7 +3830,7 @@
         <v>126914389</v>
       </c>
       <c r="B34" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>126913909</v>
       </c>
       <c r="B37" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>126914390</v>
       </c>
       <c r="B38" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>126913899</v>
       </c>
       <c r="B39" t="n">
-        <v>92808</v>
+        <v>92809</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 27566-2025 artfynd.xlsx
+++ b/artfynd/A 27566-2025 artfynd.xlsx
@@ -3729,7 +3729,7 @@
         <v>126913715</v>
       </c>
       <c r="B33" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>126914389</v>
       </c>
       <c r="B34" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>126913924</v>
       </c>
       <c r="B35" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>126913728</v>
       </c>
       <c r="B36" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>126913909</v>
       </c>
       <c r="B37" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>126914390</v>
       </c>
       <c r="B38" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>126913899</v>
       </c>
       <c r="B39" t="n">
-        <v>92809</v>
+        <v>92813</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 27566-2025 artfynd.xlsx
+++ b/artfynd/A 27566-2025 artfynd.xlsx
@@ -4143,7 +4143,7 @@
         <v>126913909</v>
       </c>
       <c r="B37" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 27566-2025 artfynd.xlsx
+++ b/artfynd/A 27566-2025 artfynd.xlsx
@@ -3729,7 +3729,7 @@
         <v>126913715</v>
       </c>
       <c r="B33" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>126914389</v>
       </c>
       <c r="B34" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>126913924</v>
       </c>
       <c r="B35" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>126913728</v>
       </c>
       <c r="B36" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>126913909</v>
       </c>
       <c r="B37" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>126914390</v>
       </c>
       <c r="B38" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>126913899</v>
       </c>
       <c r="B39" t="n">
-        <v>92813</v>
+        <v>92815</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 27566-2025 artfynd.xlsx
+++ b/artfynd/A 27566-2025 artfynd.xlsx
@@ -4341,7 +4341,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Petra Wikström, Viktoria Sturk, Marie Persson, Tomas Falk, Marlene Kangas, Christina Boyd</t>
+          <t>Petra Wikström, Christina Boyd, Marlene Kangas, Tomas Falk, Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">

--- a/artfynd/A 27566-2025 artfynd.xlsx
+++ b/artfynd/A 27566-2025 artfynd.xlsx
@@ -3729,7 +3729,7 @@
         <v>126913715</v>
       </c>
       <c r="B33" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>126914389</v>
       </c>
       <c r="B34" t="n">
-        <v>92622</v>
+        <v>92609</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>126913924</v>
       </c>
       <c r="B35" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>126913728</v>
       </c>
       <c r="B36" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>126913909</v>
       </c>
       <c r="B37" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>126914390</v>
       </c>
       <c r="B38" t="n">
-        <v>92622</v>
+        <v>92609</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Petra Wikström, Christina Boyd, Marlene Kangas, Tomas Falk, Marie Persson, Viktoria Sturk</t>
+          <t>Petra Wikström, Viktoria Sturk, Marie Persson, Tomas Falk, Marlene Kangas, Christina Boyd</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4355,7 +4355,7 @@
         <v>126913899</v>
       </c>
       <c r="B39" t="n">
-        <v>92815</v>
+        <v>92802</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 27566-2025 artfynd.xlsx
+++ b/artfynd/A 27566-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121079527</v>
+        <v>121079631</v>
       </c>
       <c r="B2" t="n">
-        <v>91980</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -722,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>887046</v>
+        <v>887079</v>
       </c>
       <c r="R2" t="n">
-        <v>7417786</v>
+        <v>7417749</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -778,44 +773,39 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Marie Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121078530</v>
+        <v>121079653</v>
       </c>
       <c r="B3" t="n">
-        <v>91986</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>887113</v>
+        <v>887091</v>
       </c>
       <c r="R3" t="n">
-        <v>7417844</v>
+        <v>7417710</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -888,22 +878,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren, Marie Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121079535</v>
+        <v>126911399</v>
       </c>
       <c r="B4" t="n">
-        <v>91978</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,44 +896,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>112</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Pikkupullinki, Nb</t>
+          <t>Pikku pulinki, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>887046</v>
+        <v>887200</v>
       </c>
       <c r="R4" t="n">
-        <v>7417786</v>
+        <v>7417955</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,12 +950,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,67 +964,77 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Christina Boyd, Jenny Hjelm Córdoba, Marie Persson, Marlene Kangas, Cecilia Rastad, Petya Valcheva, Petra Wikström, Viktoria Sturk, Tomas Falk, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125831667</v>
+        <v>121079311</v>
       </c>
       <c r="B5" t="n">
-        <v>92535</v>
+        <v>93185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>149</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Pullinkinrova, Nb</t>
+          <t>Pikkupullinki, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>887006</v>
+        <v>887116</v>
       </c>
       <c r="R5" t="n">
-        <v>7417851</v>
+        <v>7417692</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1070,12 +1058,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1084,66 +1072,67 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125831666</v>
+        <v>125949003</v>
       </c>
       <c r="B6" t="n">
-        <v>92535</v>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Pullinkinrova, Nb</t>
+          <t>Pikku pullinki, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>886946</v>
+        <v>886978</v>
       </c>
       <c r="R6" t="n">
-        <v>7417733</v>
+        <v>7417839</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1187,22 +1176,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125831653</v>
+        <v>125831642</v>
       </c>
       <c r="B7" t="n">
-        <v>92727</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1210,21 +1199,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2079</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>887230</v>
+        <v>887169</v>
       </c>
       <c r="R7" t="n">
-        <v>7417766</v>
+        <v>7417875</v>
       </c>
       <c r="S7" t="n">
         <v>2</v>
@@ -1296,48 +1285,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125831670</v>
+        <v>125948966</v>
       </c>
       <c r="B8" t="n">
-        <v>92535</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Pullinkinrova, Nb</t>
+          <t>Pikku pullinki, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>887002</v>
+        <v>887008</v>
       </c>
       <c r="R8" t="n">
-        <v>7417848</v>
+        <v>7417850</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1381,60 +1370,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125831648</v>
+        <v>125948996</v>
       </c>
       <c r="B9" t="n">
-        <v>98382</v>
+        <v>92083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>1503</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Pullinkinrova, Nb</t>
+          <t>Pikku pullinki, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>887197</v>
+        <v>887243</v>
       </c>
       <c r="R9" t="n">
-        <v>7417856</v>
+        <v>7417784</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1478,60 +1467,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125831655</v>
+        <v>125948997</v>
       </c>
       <c r="B10" t="n">
-        <v>92727</v>
+        <v>92083</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Pullinkinrova, Nb</t>
+          <t>Pikku pullinki, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>886987</v>
+        <v>886998</v>
       </c>
       <c r="R10" t="n">
-        <v>7417736</v>
+        <v>7417761</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1575,60 +1564,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125831642</v>
+        <v>125948998</v>
       </c>
       <c r="B11" t="n">
-        <v>91245</v>
+        <v>92083</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1503</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Pullinkinrova, Nb</t>
+          <t>Pikku pullinki, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>887169</v>
+        <v>886916</v>
       </c>
       <c r="R11" t="n">
-        <v>7417875</v>
+        <v>7417844</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1672,60 +1661,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125831664</v>
+        <v>125948999</v>
       </c>
       <c r="B12" t="n">
-        <v>92535</v>
+        <v>92083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Pullinkinrova, Nb</t>
+          <t>Pikku pullinki, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>887026</v>
+        <v>886955</v>
       </c>
       <c r="R12" t="n">
-        <v>7417736</v>
+        <v>7417864</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1769,60 +1758,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125831649</v>
+        <v>125948964</v>
       </c>
       <c r="B13" t="n">
-        <v>79987</v>
+        <v>92097</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>1588</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Pullinkinrova, Nb</t>
+          <t>Pikku pullinki, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>887098</v>
+        <v>887119</v>
       </c>
       <c r="R13" t="n">
-        <v>7417856</v>
+        <v>7417657</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1866,60 +1855,67 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125831652</v>
+        <v>121079578</v>
       </c>
       <c r="B14" t="n">
-        <v>97245</v>
+        <v>90932</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>1962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Pullinkinrova, Nb</t>
+          <t>Pikkupullinki, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>887148</v>
+        <v>887054</v>
       </c>
       <c r="R14" t="n">
-        <v>7417861</v>
+        <v>7417772</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1943,12 +1939,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1957,28 +1953,29 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Patrik Nygren, Marie Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125831645</v>
+        <v>121079635</v>
       </c>
       <c r="B15" t="n">
-        <v>57817</v>
+        <v>90932</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1986,37 +1983,44 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Pullinkinrova, Nb</t>
+          <t>Pikkupullinki, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>887223</v>
+        <v>887079</v>
       </c>
       <c r="R15" t="n">
-        <v>7417746</v>
+        <v>7417749</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2040,12 +2044,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2054,66 +2058,74 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Patrik Nygren, Marie Persson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125948975</v>
+        <v>121079579</v>
       </c>
       <c r="B16" t="n">
-        <v>79987</v>
+        <v>91962</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>2079</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Pikku pullinki, Nb</t>
+          <t>Pikkupullinki, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>887138</v>
+        <v>887054</v>
       </c>
       <c r="R16" t="n">
-        <v>7417874</v>
+        <v>7417772</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2137,12 +2149,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2151,66 +2163,67 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Patrik Nygren, Marie Persson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125948997</v>
+        <v>125831653</v>
       </c>
       <c r="B17" t="n">
-        <v>91406</v>
+        <v>91962</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1503</v>
+        <v>2079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Pikku pullinki, Nb</t>
+          <t>Pullinkinrova, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>886998</v>
+        <v>887230</v>
       </c>
       <c r="R17" t="n">
-        <v>7417761</v>
+        <v>7417766</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2254,22 +2267,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125948978</v>
+        <v>125831654</v>
       </c>
       <c r="B18" t="n">
-        <v>92727</v>
+        <v>91962</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2297,17 +2310,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Pikku pullinki, Nb</t>
+          <t>Pullinkinrova, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>886912</v>
+        <v>887211</v>
       </c>
       <c r="R18" t="n">
-        <v>7417840</v>
+        <v>7417803</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2351,22 +2364,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125948987</v>
+        <v>125831655</v>
       </c>
       <c r="B19" t="n">
-        <v>78738</v>
+        <v>91962</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2374,37 +2387,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Pikku pullinki, Nb</t>
+          <t>Pullinkinrova, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>886908</v>
+        <v>886987</v>
       </c>
       <c r="R19" t="n">
-        <v>7417842</v>
+        <v>7417736</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2448,22 +2461,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125948979</v>
+        <v>125831656</v>
       </c>
       <c r="B20" t="n">
-        <v>92727</v>
+        <v>91962</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2491,17 +2504,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Pikku pullinki, Nb</t>
+          <t>Pullinkinrova, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>887056</v>
+        <v>886938</v>
       </c>
       <c r="R20" t="n">
-        <v>7417834</v>
+        <v>7417878</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2545,22 +2558,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125948966</v>
+        <v>125948978</v>
       </c>
       <c r="B21" t="n">
-        <v>91245</v>
+        <v>91962</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2568,21 +2581,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>2079</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2592,10 +2605,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>887008</v>
+        <v>886912</v>
       </c>
       <c r="R21" t="n">
-        <v>7417850</v>
+        <v>7417840</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2654,10 +2667,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125948981</v>
+        <v>125948979</v>
       </c>
       <c r="B22" t="n">
-        <v>78739</v>
+        <v>91962</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2665,21 +2678,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2689,10 +2702,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>886920</v>
+        <v>887056</v>
       </c>
       <c r="R22" t="n">
-        <v>7417838</v>
+        <v>7417834</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2751,10 +2764,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125948980</v>
+        <v>126254765</v>
       </c>
       <c r="B23" t="n">
-        <v>78739</v>
+        <v>91962</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2762,37 +2775,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Pikku pullinki, Nb</t>
+          <t>Pullinkinrova, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>887085</v>
+        <v>887099</v>
       </c>
       <c r="R23" t="n">
-        <v>7417661</v>
+        <v>7417582</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2816,12 +2829,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2836,22 +2849,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125948982</v>
+        <v>126913899</v>
       </c>
       <c r="B24" t="n">
-        <v>78739</v>
+        <v>91962</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2859,37 +2872,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Pikku pullinki, Nb</t>
+          <t>Pikku Pullinki, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>887109</v>
+        <v>887048</v>
       </c>
       <c r="R24" t="n">
-        <v>7417862</v>
+        <v>7417840</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2913,12 +2926,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2933,22 +2946,26 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125948983</v>
+        <v>125948974</v>
       </c>
       <c r="B25" t="n">
-        <v>80083</v>
+        <v>80433</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2956,21 +2973,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2980,10 +2997,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>887190</v>
+        <v>887197</v>
       </c>
       <c r="R25" t="n">
-        <v>7417855</v>
+        <v>7417856</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3042,48 +3059,55 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125949005</v>
+        <v>121079535</v>
       </c>
       <c r="B26" t="n">
-        <v>92535</v>
+        <v>93189</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Pikku pullinki, Nb</t>
+          <t>Pikkupullinki, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>887242</v>
+        <v>887046</v>
       </c>
       <c r="R26" t="n">
-        <v>7417747</v>
+        <v>7417786</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3107,12 +3131,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3121,28 +3145,29 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125948964</v>
+        <v>121079668</v>
       </c>
       <c r="B27" t="n">
-        <v>91420</v>
+        <v>93189</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3150,37 +3175,44 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1588</v>
+        <v>4361</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Pikku pullinki, Nb</t>
+          <t>Pikkupullinki, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>887119</v>
+        <v>887144</v>
       </c>
       <c r="R27" t="n">
-        <v>7417657</v>
+        <v>7417648</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3204,12 +3236,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3218,28 +3250,29 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125948974</v>
+        <v>121079680</v>
       </c>
       <c r="B28" t="n">
-        <v>80084</v>
+        <v>93189</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3247,37 +3280,44 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>4361</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Pikku pullinki, Nb</t>
+          <t>Pikkupullinki, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>887197</v>
+        <v>887191</v>
       </c>
       <c r="R28" t="n">
-        <v>7417856</v>
+        <v>7417656</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3301,12 +3341,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3315,66 +3355,74 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125948998</v>
+        <v>121079527</v>
       </c>
       <c r="B29" t="n">
-        <v>91406</v>
+        <v>93191</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1503</v>
+        <v>4362</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Pikku pullinki, Nb</t>
+          <t>Pikkupullinki, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>886916</v>
+        <v>887046</v>
       </c>
       <c r="R29" t="n">
-        <v>7417844</v>
+        <v>7417786</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3398,12 +3446,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3412,28 +3460,29 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125948968</v>
+        <v>121079664</v>
       </c>
       <c r="B30" t="n">
-        <v>57657</v>
+        <v>93191</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3441,37 +3490,44 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Pikku pullinki, Nb</t>
+          <t>Pikkupullinki, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>887185</v>
+        <v>887135</v>
       </c>
       <c r="R30" t="n">
-        <v>7417849</v>
+        <v>7417668</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3495,17 +3551,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Födosök gran</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3514,66 +3565,74 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125948992</v>
+        <v>121078530</v>
       </c>
       <c r="B31" t="n">
-        <v>98361</v>
+        <v>93197</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Pikku pullinki, Nb</t>
+          <t>Pikkupullinki, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>887185</v>
+        <v>887113</v>
       </c>
       <c r="R31" t="n">
-        <v>7417856</v>
+        <v>7417844</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3597,12 +3656,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3611,32 +3670,33 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126254767</v>
+        <v>125831664</v>
       </c>
       <c r="B32" t="n">
-        <v>92535</v>
+        <v>93197</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3664,13 +3724,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>887314</v>
+        <v>887026</v>
       </c>
       <c r="R32" t="n">
-        <v>7417479</v>
+        <v>7417736</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3694,12 +3754,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3726,10 +3786,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126913715</v>
+        <v>125831666</v>
       </c>
       <c r="B33" t="n">
-        <v>80123</v>
+        <v>93197</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3737,37 +3797,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Pikku Pulinki, Nb</t>
+          <t>Pullinkinrova, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>887186</v>
+        <v>886946</v>
       </c>
       <c r="R33" t="n">
-        <v>7417858</v>
+        <v>7417733</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3791,12 +3851,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3811,30 +3871,26 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126914389</v>
+        <v>125831667</v>
       </c>
       <c r="B34" t="n">
-        <v>92622</v>
+        <v>93197</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -3858,17 +3914,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Pikku pulinki, Nb</t>
+          <t>Pullinkinrova, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>887042</v>
+        <v>887006</v>
       </c>
       <c r="R34" t="n">
-        <v>7417811</v>
+        <v>7417851</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3892,22 +3948,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:13</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:13</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3922,26 +3968,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Petra Wikström, Viktoria Sturk, Marie Persson, Tomas Falk, Marlene Kangas, Christina Boyd</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126913924</v>
+        <v>125831670</v>
       </c>
       <c r="B35" t="n">
-        <v>79020</v>
+        <v>93197</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3949,37 +3991,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Pikku Pullinki, Nb</t>
+          <t>Pullinkinrova, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>887181</v>
+        <v>887002</v>
       </c>
       <c r="R35" t="n">
-        <v>7417925</v>
+        <v>7417848</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4003,12 +4045,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4031,18 +4073,14 @@
           <t>Viktoria Sturk</t>
         </is>
       </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126913728</v>
+        <v>125949005</v>
       </c>
       <c r="B36" t="n">
-        <v>79020</v>
+        <v>93197</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4050,37 +4088,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Pikku Pulinki, Nb</t>
+          <t>Pikku pullinki, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>887153</v>
+        <v>887242</v>
       </c>
       <c r="R36" t="n">
-        <v>7417904</v>
+        <v>7417747</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4104,12 +4142,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4124,64 +4162,60 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126913909</v>
+        <v>126254767</v>
       </c>
       <c r="B37" t="n">
-        <v>98450</v>
+        <v>93197</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Pikku Pullinki, Nb</t>
+          <t>Pullinkinrova, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>887135</v>
+        <v>887314</v>
       </c>
       <c r="R37" t="n">
-        <v>7417886</v>
+        <v>7417479</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4205,12 +4239,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4233,22 +4267,18 @@
           <t>Viktoria Sturk</t>
         </is>
       </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126914390</v>
+        <v>126914389</v>
       </c>
       <c r="B38" t="n">
-        <v>92622</v>
+        <v>93197</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4276,10 +4306,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>887090</v>
+        <v>887042</v>
       </c>
       <c r="R38" t="n">
-        <v>7417868</v>
+        <v>7417811</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4311,7 +4341,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4321,7 +4351,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4341,7 +4371,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Petra Wikström, Christina Boyd, Marlene Kangas, Tomas Falk, Marie Persson, Viktoria Sturk</t>
+          <t>Petra Wikström, Viktoria Sturk, Marie Persson, Tomas Falk, Marlene Kangas, Christina Boyd</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4352,10 +4382,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126913899</v>
+        <v>126914390</v>
       </c>
       <c r="B39" t="n">
-        <v>92815</v>
+        <v>93197</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4363,34 +4393,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Pikku Pullinki, Nb</t>
+          <t>Pikku pulinki, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>887048</v>
+        <v>887090</v>
       </c>
       <c r="R39" t="n">
-        <v>7417840</v>
+        <v>7417868</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4420,9 +4450,19 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4437,15 +4477,3030 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Petra Wikström, Viktoria Sturk, Marie Persson, Tomas Falk, Marlene Kangas, Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>121079662</v>
+      </c>
+      <c r="B40" t="n">
+        <v>92841</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Pikkupullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>887135</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7417668</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Patrik Nygren, Sirirat Chanon</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>125948965</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Pikku pullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>887242</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7417784</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>121079661</v>
+      </c>
+      <c r="B42" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Pikkupullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>887135</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7417668</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Patrik Nygren, Sirirat Chanon</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>125831660</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Pullinkinrova, Nb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>886979</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7417844</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
           <t>Viktoria Sturk</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
+      <c r="AX43" t="inlineStr">
         <is>
           <t>Viktoria Sturk</t>
         </is>
       </c>
-      <c r="AY39" t="inlineStr">
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>125949001</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Pikku pullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>886932</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7417728</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>126913728</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Pikku Pulinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>887153</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7417904</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>126913924</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Pikku Pullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>887181</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7417925</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>119676961</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Pullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>887272</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7417781</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>125948987</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Pikku pullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>886908</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7417842</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>125948989</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Pikku pullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>886952</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7417862</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>126913695</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Pikku Pulinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>887071</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7417814</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>126914337</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Pikku pulinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>887078</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7417772</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Petra Wikström, Viktoria Sturk, Marie Persson, Tomas Falk, Marlene Kangas, Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>125831649</v>
+      </c>
+      <c r="B52" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Pullinkinrova, Nb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>887098</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7417856</v>
+      </c>
+      <c r="S52" t="n">
+        <v>2</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>125948975</v>
+      </c>
+      <c r="B53" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Pikku pullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>887138</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7417874</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>125948983</v>
+      </c>
+      <c r="B54" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Pikku pullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>887190</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7417855</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>126913715</v>
+      </c>
+      <c r="B55" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Pikku Pulinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>887186</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7417858</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>126915381</v>
+      </c>
+      <c r="B56" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Pikku pullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>887199</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7417947</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>125948968</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Pikku pullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>887185</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7417849</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Födosök gran</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>125831644</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Pullinkinrova, Nb</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>886985</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7417844</v>
+      </c>
+      <c r="S58" t="n">
+        <v>2</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>126254764</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Pullinkinrova, Nb</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>887268</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7417606</v>
+      </c>
+      <c r="S59" t="n">
+        <v>1</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>126914348</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Pikku pulinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>887207</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7417796</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Petra Wikström, Viktoria Sturk, Marie Persson, Tomas Falk, Marlene Kangas, Christina Boyd, Viktoria Sturk, Marie Persson, Tomas Falk, Marlene Kangas, Christina Boyd, Viktoria Sturk, Marie Persson, Tomas Falk, Marlene Kangas, Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>125831645</v>
+      </c>
+      <c r="B61" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Pullinkinrova, Nb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>887223</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7417746</v>
+      </c>
+      <c r="S61" t="n">
+        <v>2</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>125948992</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Pikku pullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>887185</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7417856</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>126913909</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Pikku Pullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>887135</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7417886</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>125831652</v>
+      </c>
+      <c r="B64" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Pullinkinrova, Nb</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>887148</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7417861</v>
+      </c>
+      <c r="S64" t="n">
+        <v>2</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>125831648</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Pullinkinrova, Nb</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>887197</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7417856</v>
+      </c>
+      <c r="S65" t="n">
+        <v>2</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>125948980</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Pikku pullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>887085</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7417661</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>125948981</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Pikku pullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>886920</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7417838</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>125948982</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Pikku pullinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>887109</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7417862</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>126914358</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Pikku pulinki, Nb</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>887065</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7417785</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Petra Wikström, Viktoria Sturk, Marie Persson, Tomas Falk, Marlene Kangas, Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
         <is>
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>

--- a/artfynd/A 27566-2025 artfynd.xlsx
+++ b/artfynd/A 27566-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AZ69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121079631</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121079653</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126911399</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121079311</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1185,6 +1210,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125949003</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1282,6 +1312,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831642</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125948966</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1476,6 +1516,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125948996</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1573,6 +1618,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125948997</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1670,6 +1720,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125948998</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1767,6 +1822,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125948999</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1864,6 +1924,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125948964</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1969,6 +2034,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121079578</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2074,6 +2144,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121079635</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2179,6 +2254,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121079579</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2276,6 +2356,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831653</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2373,6 +2458,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831654</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2470,6 +2560,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831655</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2567,6 +2662,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831656</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2664,6 +2764,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125948978</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2761,6 +2866,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125948979</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2858,6 +2968,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126254765</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2959,6 +3074,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126913899</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3056,6 +3176,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125948974</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3161,6 +3286,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121079535</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3266,6 +3396,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121079668</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3371,6 +3506,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121079680</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3476,6 +3616,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121079527</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3581,6 +3726,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121079664</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3686,6 +3836,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121078530</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3783,6 +3938,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831664</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3880,6 +4040,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831666</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3977,6 +4142,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831667</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4074,6 +4244,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831670</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4171,6 +4346,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125949005</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4268,6 +4448,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126254767</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4379,6 +4564,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126914389</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4490,6 +4680,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126914390</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4595,6 +4790,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121079662</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4692,6 +4892,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125948965</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4797,6 +5002,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121079661</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4894,6 +5104,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831660</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4991,6 +5206,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125949001</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5092,6 +5312,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126913728</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5193,6 +5418,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126913924</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5290,6 +5520,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119676961</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5387,6 +5622,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125948987</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5484,6 +5724,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125948989</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5585,6 +5830,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126913695</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5696,6 +5946,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126914337</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5793,6 +6048,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831649</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5890,6 +6150,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125948975</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5987,6 +6252,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125948983</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6088,6 +6358,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126913715</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6189,6 +6464,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126915381</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6291,6 +6571,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125948968</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6393,6 +6678,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831644</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6495,6 +6785,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126254764</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6614,6 +6909,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126914348</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6711,6 +7011,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831645</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6808,6 +7113,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125948992</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6909,6 +7219,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126913909</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7006,6 +7321,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831652</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7103,6 +7423,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831648</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7200,6 +7525,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125948980</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7297,6 +7627,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125948981</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7394,6 +7729,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125948982</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7505,8 +7845,83 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126914358</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>